--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/MOLA - 26_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/MOLA - 26_01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,7 +452,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -478,11 +472,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -503,7 +492,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -524,7 +512,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -545,7 +532,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -566,7 +552,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -583,7 +568,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -596,7 +580,6 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
